--- a/artfynd/A 18078-2023 artfynd.xlsx
+++ b/artfynd/A 18078-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18078-2023 artfynd.xlsx
+++ b/artfynd/A 18078-2023 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117952855</v>
+        <v>117950716</v>
       </c>
       <c r="B5" t="n">
-        <v>97871</v>
+        <v>108703</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,23 +1038,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223619</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607985</v>
+        <v>607922</v>
       </c>
       <c r="R5" t="n">
-        <v>6560303</v>
+        <v>6560341</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,9 +1118,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1134,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117950716</v>
+        <v>117952855</v>
       </c>
       <c r="B6" t="n">
-        <v>108703</v>
+        <v>97871</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,27 +1150,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>223619</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607922</v>
+        <v>607985</v>
       </c>
       <c r="R6" t="n">
-        <v>6560341</v>
+        <v>6560303</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,9 +1226,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 18078-2023 artfynd.xlsx
+++ b/artfynd/A 18078-2023 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117950716</v>
+        <v>117952855</v>
       </c>
       <c r="B5" t="n">
-        <v>108703</v>
+        <v>97873</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,27 +1038,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>223619</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607922</v>
+        <v>607985</v>
       </c>
       <c r="R5" t="n">
-        <v>6560341</v>
+        <v>6560303</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,9 +1114,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117952855</v>
+        <v>117950716</v>
       </c>
       <c r="B6" t="n">
-        <v>97871</v>
+        <v>108705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,23 +1146,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223619</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607985</v>
+        <v>607922</v>
       </c>
       <c r="R6" t="n">
-        <v>6560303</v>
+        <v>6560341</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,9 +1226,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 18078-2023 artfynd.xlsx
+++ b/artfynd/A 18078-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1737413</v>
+        <v>105314501</v>
       </c>
       <c r="B2" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallbacken, 400 m NO om, Srm</t>
+          <t>Vatthällen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608085.8150067613</v>
+        <v>607172</v>
       </c>
       <c r="R2" t="n">
-        <v>6560300.913302329</v>
+        <v>6560670</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-10-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +757,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>ört-mossrik sandbarrskog</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105314501</v>
+        <v>105316105</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607171.5714306926</v>
+        <v>607174</v>
       </c>
       <c r="R3" t="n">
-        <v>6560669.548203175</v>
+        <v>6560666</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +879,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105316105</v>
+        <v>117950716</v>
       </c>
       <c r="B4" t="n">
-        <v>4808</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vatthällen, Srm</t>
+          <t>Tallbacken 600m NNO om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607173.7258814663</v>
+        <v>607922</v>
       </c>
       <c r="R4" t="n">
-        <v>6560666.018466134</v>
+        <v>6560341</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,73 +962,77 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117952855</v>
+        <v>110914532</v>
       </c>
       <c r="B5" t="n">
-        <v>97881</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223619</v>
+        <v>221317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallbacken 600m NNO om, Srm</t>
+          <t>Kräftbäcken 250 m N, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607985</v>
+        <v>608051</v>
       </c>
       <c r="R5" t="n">
-        <v>6560303</v>
+        <v>6560093</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,12 +1059,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>stor mängd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,35 +1082,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>urbruktaget grustag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Kerstin Frostberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Kerstin Frostberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117950716</v>
+        <v>111441276</v>
       </c>
       <c r="B6" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,14 +1137,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallbacken 600m NNO om, Srm</t>
+          <t>Vatthällen 250 m OSO, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607922</v>
+        <v>607230</v>
       </c>
       <c r="R6" t="n">
-        <v>6560341</v>
+        <v>6560626</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,12 +1171,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera spridda bestånd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,27 +1190,366 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Grässlänt med sandblottor.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117952855</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tallbacken 600m NNO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>607985</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6560303</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77080514</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>306</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svämskog, Kräftbäcken, Kräftbäcken, Dunker, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608179</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6560181</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-04-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-04-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Svämskog.</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Björk, gran, mm.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Björk, gran, mm.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fingal Gyllang, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>77080520</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svämskog, Kräftbäcken, Kräftbäcken, Dunker, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608179</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6560181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-04-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-04-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Svämskog.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fingal Gyllang, Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18078-2023 artfynd.xlsx
+++ b/artfynd/A 18078-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77080514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314501</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77080520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117950716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914532</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111441276</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,8 +1590,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117952855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>